--- a/public/M15A上班時間調動表.xlsx
+++ b/public/M15A上班時間調動表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kyler\OneDrive\桌面\mss_ai_department\mss_ai_department\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AB6327D-64A9-4A9A-B574-B56BE6DC2F5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEAD598C-6D96-424C-9003-3D74790E5452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1610" yWindow="2230" windowWidth="14400" windowHeight="8170" tabRatio="599" xr2:uid="{99967081-488D-44D6-94DC-7450F6337A9B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="599" xr2:uid="{99967081-488D-44D6-94DC-7450F6337A9B}"/>
   </bookViews>
   <sheets>
     <sheet name="M15A上班時間調動表" sheetId="56" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="30">
   <si>
     <t>處/機關：</t>
   </si>
@@ -202,7 +202,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m&quot;月&quot;d&quot;日&quot;"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="12"/>
       <name val="新細明體"/>
@@ -248,13 +248,6 @@
       <charset val="136"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <family val="1"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -992,7 +985,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -1082,17 +1075,176 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="37" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1109,227 +1261,68 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="37" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2335,83 +2328,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21.5">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="104"/>
-      <c r="C1" s="104"/>
-      <c r="D1" s="104"/>
-      <c r="E1" s="104"/>
-      <c r="F1" s="104"/>
-      <c r="G1" s="104"/>
-      <c r="H1" s="104"/>
-      <c r="I1" s="105"/>
-      <c r="K1" s="103" t="s">
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
+      <c r="K1" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="104"/>
-      <c r="M1" s="104"/>
-      <c r="N1" s="104"/>
-      <c r="O1" s="104"/>
-      <c r="P1" s="104"/>
-      <c r="Q1" s="104"/>
-      <c r="R1" s="104"/>
-      <c r="S1" s="105"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="30"/>
+      <c r="R1" s="30"/>
+      <c r="S1" s="31"/>
     </row>
     <row r="2" spans="1:19" ht="22" thickBot="1">
-      <c r="A2" s="106" t="s">
+      <c r="A2" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="107"/>
-      <c r="C2" s="107"/>
-      <c r="D2" s="107"/>
-      <c r="E2" s="107"/>
-      <c r="F2" s="107"/>
-      <c r="G2" s="107"/>
-      <c r="H2" s="107"/>
-      <c r="I2" s="108"/>
-      <c r="K2" s="106" t="s">
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="34"/>
+      <c r="K2" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="L2" s="107"/>
-      <c r="M2" s="107"/>
-      <c r="N2" s="107"/>
-      <c r="O2" s="107"/>
-      <c r="P2" s="107"/>
-      <c r="Q2" s="107"/>
-      <c r="R2" s="107"/>
-      <c r="S2" s="108"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="33"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="33"/>
+      <c r="S2" s="34"/>
     </row>
     <row r="3" spans="1:19" ht="25" customHeight="1">
-      <c r="A3" s="56">
+      <c r="A3" s="35">
         <v>1</v>
       </c>
-      <c r="B3" s="109" t="s">
+      <c r="B3" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="110"/>
-      <c r="D3" s="110"/>
-      <c r="E3" s="110"/>
-      <c r="F3" s="110"/>
-      <c r="G3" s="110"/>
-      <c r="H3" s="110"/>
-      <c r="I3" s="111"/>
-      <c r="K3" s="56">
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="40"/>
+      <c r="K3" s="35">
         <v>1</v>
       </c>
-      <c r="L3" s="109" t="s">
+      <c r="L3" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="M3" s="110"/>
-      <c r="N3" s="110"/>
-      <c r="O3" s="110"/>
-      <c r="P3" s="110"/>
-      <c r="Q3" s="110"/>
-      <c r="R3" s="110"/>
-      <c r="S3" s="111"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="39"/>
+      <c r="O3" s="39"/>
+      <c r="P3" s="39"/>
+      <c r="Q3" s="39"/>
+      <c r="R3" s="39"/>
+      <c r="S3" s="40"/>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
-      <c r="A4" s="57"/>
+      <c r="A4" s="36"/>
       <c r="B4" s="19" t="s">
         <v>9</v>
       </c>
@@ -2424,14 +2417,11 @@
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="5"/>
-      <c r="K4" s="57"/>
+      <c r="K4" s="36"/>
       <c r="L4" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="19" t="str">
-        <f>IF(C4="","",C4)</f>
-        <v/>
-      </c>
+      <c r="M4" s="19"/>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
       <c r="P4" s="19"/>
@@ -2439,13 +2429,10 @@
         <v>0</v>
       </c>
       <c r="R4" s="4"/>
-      <c r="S4" s="5" t="str">
-        <f>IF(I4="","",I4)</f>
-        <v/>
-      </c>
+      <c r="S4" s="5"/>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1" thickBot="1">
-      <c r="A5" s="58"/>
+      <c r="A5" s="37"/>
       <c r="B5" s="21" t="s">
         <v>10</v>
       </c>
@@ -2458,14 +2445,11 @@
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="3"/>
-      <c r="K5" s="58"/>
+      <c r="K5" s="37"/>
       <c r="L5" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="M5" s="21" t="str">
-        <f>IF(C5="","",C5)</f>
-        <v/>
-      </c>
+      <c r="M5" s="21"/>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" s="21"/>
@@ -2473,13 +2457,10 @@
         <v>11</v>
       </c>
       <c r="R5" s="2"/>
-      <c r="S5" s="3" t="str">
-        <f>IF(I5="","",I5)</f>
-        <v/>
-      </c>
+      <c r="S5" s="3"/>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
-      <c r="A6" s="46">
+      <c r="A6" s="65">
         <v>2</v>
       </c>
       <c r="B6" s="15" t="s">
@@ -2492,7 +2473,7 @@
       <c r="G6" s="15"/>
       <c r="H6" s="15"/>
       <c r="I6" s="16"/>
-      <c r="K6" s="46">
+      <c r="K6" s="65">
         <v>2</v>
       </c>
       <c r="L6" s="15" t="s">
@@ -2507,7 +2488,7 @@
       <c r="S6" s="16"/>
     </row>
     <row r="7" spans="1:19" ht="32.25" customHeight="1">
-      <c r="A7" s="46"/>
+      <c r="A7" s="65"/>
       <c r="B7" s="19" t="s">
         <v>13</v>
       </c>
@@ -2515,14 +2496,14 @@
       <c r="D7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="101"/>
-      <c r="F7" s="101"/>
-      <c r="G7" s="101"/>
-      <c r="H7" s="101"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
+      <c r="H7" s="66"/>
       <c r="I7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="K7" s="46"/>
+      <c r="K7" s="65"/>
       <c r="L7" s="19" t="s">
         <v>13</v>
       </c>
@@ -2530,19 +2511,16 @@
       <c r="N7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="O7" s="101" t="str">
-        <f>IF(E7="","",E7)</f>
-        <v/>
-      </c>
-      <c r="P7" s="101"/>
-      <c r="Q7" s="101"/>
-      <c r="R7" s="101"/>
+      <c r="O7" s="66"/>
+      <c r="P7" s="66"/>
+      <c r="Q7" s="66"/>
+      <c r="R7" s="66"/>
       <c r="S7" s="5" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="37.5" customHeight="1">
-      <c r="A8" s="46"/>
+      <c r="A8" s="65"/>
       <c r="B8" s="19" t="s">
         <v>16</v>
       </c>
@@ -2553,14 +2531,11 @@
       <c r="G8" s="1"/>
       <c r="H8" s="4"/>
       <c r="I8" s="5"/>
-      <c r="K8" s="46"/>
+      <c r="K8" s="65"/>
       <c r="L8" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="M8" s="19" t="str">
-        <f>IF(C8="","",C8)</f>
-        <v/>
-      </c>
+      <c r="M8" s="19"/>
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
       <c r="P8" s="1"/>
@@ -2569,44 +2544,44 @@
       <c r="S8" s="5"/>
     </row>
     <row r="9" spans="1:19" ht="25" customHeight="1">
-      <c r="A9" s="46"/>
+      <c r="A9" s="65"/>
       <c r="B9" s="19"/>
-      <c r="C9" s="102" t="s">
+      <c r="C9" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="52"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="52"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
       <c r="G9" s="6"/>
-      <c r="H9" s="47" t="s">
+      <c r="H9" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="I9" s="48"/>
-      <c r="K9" s="46"/>
+      <c r="I9" s="69"/>
+      <c r="K9" s="65"/>
       <c r="L9" s="19"/>
-      <c r="M9" s="102" t="s">
+      <c r="M9" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="N9" s="52"/>
-      <c r="O9" s="52"/>
-      <c r="P9" s="52"/>
+      <c r="N9" s="44"/>
+      <c r="O9" s="44"/>
+      <c r="P9" s="44"/>
       <c r="Q9" s="6"/>
-      <c r="R9" s="47" t="s">
+      <c r="R9" s="68" t="s">
         <v>3</v>
       </c>
-      <c r="S9" s="48"/>
+      <c r="S9" s="69"/>
     </row>
     <row r="10" spans="1:19" ht="25" customHeight="1">
-      <c r="A10" s="46"/>
+      <c r="A10" s="65"/>
       <c r="B10" s="7"/>
-      <c r="C10" s="49" t="s">
+      <c r="C10" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="50"/>
-      <c r="E10" s="51" t="s">
+      <c r="D10" s="42"/>
+      <c r="E10" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="F10" s="52"/>
+      <c r="F10" s="44"/>
       <c r="G10" s="6"/>
       <c r="H10" s="8" t="s">
         <v>1</v>
@@ -2614,16 +2589,16 @@
       <c r="I10" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="K10" s="46"/>
+      <c r="K10" s="65"/>
       <c r="L10" s="7"/>
-      <c r="M10" s="49" t="s">
+      <c r="M10" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="N10" s="50"/>
-      <c r="O10" s="51" t="s">
+      <c r="N10" s="42"/>
+      <c r="O10" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="P10" s="52"/>
+      <c r="P10" s="44"/>
       <c r="Q10" s="6"/>
       <c r="R10" s="8" t="s">
         <v>1</v>
@@ -2633,366 +2608,345 @@
       </c>
     </row>
     <row r="11" spans="1:19" ht="28" customHeight="1">
-      <c r="A11" s="46"/>
-      <c r="B11" s="62">
+      <c r="A11" s="65"/>
+      <c r="B11" s="45">
         <v>1</v>
       </c>
-      <c r="C11" s="65" t="s">
+      <c r="C11" s="101" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="96"/>
-      <c r="E11" s="87"/>
-      <c r="F11" s="72"/>
+      <c r="D11" s="102"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="49"/>
       <c r="G11" s="10"/>
-      <c r="H11" s="77" t="s">
+      <c r="H11" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="I11" s="83"/>
-      <c r="K11" s="46"/>
-      <c r="L11" s="62">
+      <c r="I11" s="57"/>
+      <c r="K11" s="65"/>
+      <c r="L11" s="45">
         <v>1</v>
       </c>
-      <c r="M11" s="65" t="str">
+      <c r="M11" s="101" t="str">
         <f>C11</f>
         <v xml:space="preserve"> 年  月  日</v>
       </c>
-      <c r="N11" s="66"/>
-      <c r="O11" s="87" t="str">
-        <f>IF(E11="","",E11)</f>
-        <v/>
-      </c>
-      <c r="P11" s="91"/>
+      <c r="N11" s="107"/>
+      <c r="O11" s="48"/>
+      <c r="P11" s="60"/>
       <c r="Q11" s="10"/>
-      <c r="R11" s="77" t="str">
-        <f>H11</f>
-        <v xml:space="preserve"> 年  月  日</v>
-      </c>
-      <c r="S11" s="83" t="str">
-        <f>IF(I11="","",I11)</f>
-        <v/>
-      </c>
+      <c r="R11" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="S11" s="57"/>
     </row>
     <row r="12" spans="1:19" ht="28" customHeight="1">
-      <c r="A12" s="46"/>
-      <c r="B12" s="63"/>
-      <c r="C12" s="97"/>
-      <c r="D12" s="98"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="74"/>
+      <c r="A12" s="65"/>
+      <c r="B12" s="46"/>
+      <c r="C12" s="103"/>
+      <c r="D12" s="104"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="51"/>
       <c r="G12" s="12"/>
-      <c r="H12" s="78"/>
-      <c r="I12" s="81"/>
-      <c r="K12" s="46"/>
-      <c r="L12" s="63"/>
-      <c r="M12" s="67"/>
-      <c r="N12" s="68"/>
-      <c r="O12" s="92"/>
-      <c r="P12" s="93"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="58"/>
+      <c r="K12" s="65"/>
+      <c r="L12" s="46"/>
+      <c r="M12" s="108"/>
+      <c r="N12" s="109"/>
+      <c r="O12" s="61"/>
+      <c r="P12" s="62"/>
       <c r="Q12" s="12"/>
-      <c r="R12" s="78"/>
-      <c r="S12" s="84"/>
+      <c r="R12" s="55"/>
+      <c r="S12" s="70"/>
     </row>
     <row r="13" spans="1:19" ht="28" customHeight="1">
-      <c r="A13" s="46"/>
-      <c r="B13" s="86"/>
-      <c r="C13" s="99"/>
-      <c r="D13" s="100"/>
-      <c r="E13" s="88"/>
-      <c r="F13" s="89"/>
+      <c r="A13" s="65"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="105"/>
+      <c r="D13" s="106"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="53"/>
       <c r="G13" s="11"/>
-      <c r="H13" s="79"/>
-      <c r="I13" s="90"/>
-      <c r="K13" s="46"/>
-      <c r="L13" s="86"/>
-      <c r="M13" s="69"/>
-      <c r="N13" s="70"/>
-      <c r="O13" s="94"/>
-      <c r="P13" s="95"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="59"/>
+      <c r="K13" s="65"/>
+      <c r="L13" s="47"/>
+      <c r="M13" s="110"/>
+      <c r="N13" s="111"/>
+      <c r="O13" s="63"/>
+      <c r="P13" s="64"/>
       <c r="Q13" s="11"/>
-      <c r="R13" s="79"/>
-      <c r="S13" s="85"/>
+      <c r="R13" s="56"/>
+      <c r="S13" s="71"/>
     </row>
     <row r="14" spans="1:19" ht="28" customHeight="1">
-      <c r="A14" s="46"/>
-      <c r="B14" s="62">
+      <c r="A14" s="65"/>
+      <c r="B14" s="45">
         <v>2</v>
       </c>
-      <c r="C14" s="65" t="s">
+      <c r="C14" s="101" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="66"/>
-      <c r="E14" s="87"/>
-      <c r="F14" s="72"/>
+      <c r="D14" s="107"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="49"/>
       <c r="G14" s="10"/>
-      <c r="H14" s="77" t="s">
+      <c r="H14" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="I14" s="83"/>
-      <c r="K14" s="46"/>
-      <c r="L14" s="62">
+      <c r="I14" s="57"/>
+      <c r="K14" s="65"/>
+      <c r="L14" s="45">
         <v>2</v>
       </c>
-      <c r="M14" s="65" t="str">
+      <c r="M14" s="101" t="str">
         <f>C14</f>
         <v xml:space="preserve"> 年  月  日</v>
       </c>
-      <c r="N14" s="66"/>
-      <c r="O14" s="87" t="str">
-        <f>IF(E14="","",E14)</f>
-        <v/>
-      </c>
-      <c r="P14" s="91"/>
+      <c r="N14" s="107"/>
+      <c r="O14" s="48"/>
+      <c r="P14" s="60"/>
       <c r="Q14" s="10"/>
-      <c r="R14" s="77" t="str">
-        <f>H14</f>
-        <v xml:space="preserve"> 年  月  日</v>
-      </c>
-      <c r="S14" s="83" t="str">
-        <f>IF(I14="","",I14)</f>
-        <v/>
-      </c>
+      <c r="R14" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="S14" s="57"/>
     </row>
     <row r="15" spans="1:19" ht="28" customHeight="1">
-      <c r="A15" s="46"/>
-      <c r="B15" s="63"/>
-      <c r="C15" s="67"/>
-      <c r="D15" s="68"/>
-      <c r="E15" s="73"/>
-      <c r="F15" s="74"/>
+      <c r="A15" s="65"/>
+      <c r="B15" s="46"/>
+      <c r="C15" s="108"/>
+      <c r="D15" s="109"/>
+      <c r="E15" s="50"/>
+      <c r="F15" s="51"/>
       <c r="G15" s="12"/>
-      <c r="H15" s="78"/>
-      <c r="I15" s="81"/>
-      <c r="K15" s="46"/>
-      <c r="L15" s="63"/>
-      <c r="M15" s="67"/>
-      <c r="N15" s="68"/>
-      <c r="O15" s="92"/>
-      <c r="P15" s="93"/>
+      <c r="H15" s="55"/>
+      <c r="I15" s="58"/>
+      <c r="K15" s="65"/>
+      <c r="L15" s="46"/>
+      <c r="M15" s="108"/>
+      <c r="N15" s="109"/>
+      <c r="O15" s="61"/>
+      <c r="P15" s="62"/>
       <c r="Q15" s="12"/>
-      <c r="R15" s="78"/>
-      <c r="S15" s="84"/>
+      <c r="R15" s="55"/>
+      <c r="S15" s="70"/>
     </row>
     <row r="16" spans="1:19" ht="28" customHeight="1">
-      <c r="A16" s="46"/>
-      <c r="B16" s="86"/>
-      <c r="C16" s="69"/>
-      <c r="D16" s="70"/>
-      <c r="E16" s="88"/>
-      <c r="F16" s="89"/>
+      <c r="A16" s="65"/>
+      <c r="B16" s="47"/>
+      <c r="C16" s="110"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="53"/>
       <c r="G16" s="11"/>
-      <c r="H16" s="79"/>
-      <c r="I16" s="90"/>
-      <c r="K16" s="46"/>
-      <c r="L16" s="86"/>
-      <c r="M16" s="69"/>
-      <c r="N16" s="70"/>
-      <c r="O16" s="94"/>
-      <c r="P16" s="95"/>
+      <c r="H16" s="56"/>
+      <c r="I16" s="59"/>
+      <c r="K16" s="65"/>
+      <c r="L16" s="47"/>
+      <c r="M16" s="110"/>
+      <c r="N16" s="111"/>
+      <c r="O16" s="63"/>
+      <c r="P16" s="64"/>
       <c r="Q16" s="11"/>
-      <c r="R16" s="79"/>
-      <c r="S16" s="85"/>
+      <c r="R16" s="56"/>
+      <c r="S16" s="71"/>
     </row>
     <row r="17" spans="1:20" ht="28" customHeight="1">
-      <c r="A17" s="46"/>
-      <c r="B17" s="62">
+      <c r="A17" s="65"/>
+      <c r="B17" s="45">
         <v>3</v>
       </c>
-      <c r="C17" s="65" t="s">
+      <c r="C17" s="101" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="66"/>
-      <c r="E17" s="71"/>
-      <c r="F17" s="72"/>
+      <c r="D17" s="107"/>
+      <c r="E17" s="73"/>
+      <c r="F17" s="49"/>
       <c r="G17" s="10"/>
-      <c r="H17" s="77" t="s">
+      <c r="H17" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="I17" s="83"/>
-      <c r="K17" s="46"/>
-      <c r="L17" s="62">
+      <c r="I17" s="57"/>
+      <c r="K17" s="65"/>
+      <c r="L17" s="45">
         <v>3</v>
       </c>
-      <c r="M17" s="65" t="str">
+      <c r="M17" s="101" t="str">
         <f>C17</f>
         <v xml:space="preserve"> 年  月  日</v>
       </c>
-      <c r="N17" s="66"/>
-      <c r="O17" s="71" t="str">
-        <f>IF(E17="","",E17)</f>
-        <v/>
-      </c>
-      <c r="P17" s="72"/>
+      <c r="N17" s="107"/>
+      <c r="O17" s="73"/>
+      <c r="P17" s="49"/>
       <c r="Q17" s="10"/>
-      <c r="R17" s="77" t="str">
-        <f>H17</f>
-        <v xml:space="preserve"> 年  月  日</v>
-      </c>
-      <c r="S17" s="80" t="str">
-        <f>IF(I17="","",I17)</f>
-        <v/>
-      </c>
+      <c r="R17" s="54" t="s">
+        <v>26</v>
+      </c>
+      <c r="S17" s="77"/>
     </row>
     <row r="18" spans="1:20" ht="28" customHeight="1">
-      <c r="A18" s="46"/>
-      <c r="B18" s="63"/>
-      <c r="C18" s="67"/>
-      <c r="D18" s="68"/>
-      <c r="E18" s="73"/>
-      <c r="F18" s="74"/>
+      <c r="A18" s="65"/>
+      <c r="B18" s="46"/>
+      <c r="C18" s="108"/>
+      <c r="D18" s="109"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="51"/>
       <c r="G18" s="12"/>
-      <c r="H18" s="78"/>
-      <c r="I18" s="81"/>
-      <c r="K18" s="46"/>
-      <c r="L18" s="63"/>
-      <c r="M18" s="67"/>
-      <c r="N18" s="68"/>
-      <c r="O18" s="73"/>
-      <c r="P18" s="74"/>
+      <c r="H18" s="55"/>
+      <c r="I18" s="58"/>
+      <c r="K18" s="65"/>
+      <c r="L18" s="46"/>
+      <c r="M18" s="108"/>
+      <c r="N18" s="109"/>
+      <c r="O18" s="50"/>
+      <c r="P18" s="51"/>
       <c r="Q18" s="12"/>
-      <c r="R18" s="78"/>
-      <c r="S18" s="81"/>
+      <c r="R18" s="55"/>
+      <c r="S18" s="58"/>
     </row>
     <row r="19" spans="1:20" ht="28" customHeight="1" thickBot="1">
-      <c r="A19" s="46"/>
-      <c r="B19" s="64"/>
-      <c r="C19" s="69"/>
-      <c r="D19" s="70"/>
-      <c r="E19" s="75"/>
-      <c r="F19" s="76"/>
+      <c r="A19" s="65"/>
+      <c r="B19" s="72"/>
+      <c r="C19" s="110"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="74"/>
+      <c r="F19" s="75"/>
       <c r="G19" s="13"/>
-      <c r="H19" s="79"/>
-      <c r="I19" s="82"/>
-      <c r="K19" s="46"/>
-      <c r="L19" s="64"/>
-      <c r="M19" s="69"/>
-      <c r="N19" s="70"/>
-      <c r="O19" s="75"/>
-      <c r="P19" s="76"/>
+      <c r="H19" s="56"/>
+      <c r="I19" s="76"/>
+      <c r="K19" s="65"/>
+      <c r="L19" s="72"/>
+      <c r="M19" s="110"/>
+      <c r="N19" s="111"/>
+      <c r="O19" s="74"/>
+      <c r="P19" s="75"/>
       <c r="Q19" s="13"/>
-      <c r="R19" s="79"/>
-      <c r="S19" s="82"/>
+      <c r="R19" s="56"/>
+      <c r="S19" s="76"/>
     </row>
     <row r="20" spans="1:20" ht="20.25" customHeight="1">
-      <c r="A20" s="56">
+      <c r="A20" s="35">
         <v>3</v>
       </c>
-      <c r="B20" s="59" t="s">
+      <c r="B20" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="60"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="60"/>
-      <c r="H20" s="60"/>
-      <c r="I20" s="61"/>
-      <c r="K20" s="56">
+      <c r="C20" s="82"/>
+      <c r="D20" s="82"/>
+      <c r="E20" s="82"/>
+      <c r="F20" s="82"/>
+      <c r="G20" s="82"/>
+      <c r="H20" s="82"/>
+      <c r="I20" s="83"/>
+      <c r="K20" s="35">
         <v>3</v>
       </c>
-      <c r="L20" s="59" t="s">
+      <c r="L20" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="M20" s="60"/>
-      <c r="N20" s="60"/>
-      <c r="O20" s="60"/>
-      <c r="P20" s="60"/>
-      <c r="Q20" s="60"/>
-      <c r="R20" s="60"/>
-      <c r="S20" s="61"/>
+      <c r="M20" s="82"/>
+      <c r="N20" s="82"/>
+      <c r="O20" s="82"/>
+      <c r="P20" s="82"/>
+      <c r="Q20" s="82"/>
+      <c r="R20" s="82"/>
+      <c r="S20" s="83"/>
     </row>
     <row r="21" spans="1:20" ht="45" customHeight="1">
-      <c r="A21" s="57"/>
-      <c r="B21" s="44" t="s">
+      <c r="A21" s="36"/>
+      <c r="B21" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="45"/>
-      <c r="D21" s="33" t="s">
+      <c r="C21" s="85"/>
+      <c r="D21" s="86" t="s">
         <v>22</v>
       </c>
-      <c r="E21" s="34"/>
-      <c r="F21" s="35" t="s">
+      <c r="E21" s="87"/>
+      <c r="F21" s="88" t="s">
         <v>20</v>
       </c>
-      <c r="G21" s="36"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="37"/>
-      <c r="K21" s="57"/>
-      <c r="L21" s="44" t="s">
+      <c r="G21" s="89"/>
+      <c r="H21" s="89"/>
+      <c r="I21" s="90"/>
+      <c r="K21" s="36"/>
+      <c r="L21" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="M21" s="45"/>
-      <c r="N21" s="33" t="s">
+      <c r="M21" s="85"/>
+      <c r="N21" s="86" t="s">
         <v>22</v>
       </c>
-      <c r="O21" s="34"/>
-      <c r="P21" s="35" t="s">
+      <c r="O21" s="87"/>
+      <c r="P21" s="88" t="s">
         <v>20</v>
       </c>
-      <c r="Q21" s="36"/>
-      <c r="R21" s="36"/>
-      <c r="S21" s="37"/>
+      <c r="Q21" s="89"/>
+      <c r="R21" s="89"/>
+      <c r="S21" s="90"/>
     </row>
     <row r="22" spans="1:20" ht="63.75" customHeight="1">
-      <c r="A22" s="57"/>
-      <c r="B22" s="29"/>
-      <c r="C22" s="30"/>
+      <c r="A22" s="36"/>
+      <c r="B22" s="96"/>
+      <c r="C22" s="97"/>
       <c r="D22" s="24"/>
       <c r="E22" s="11"/>
-      <c r="F22" s="53" t="s">
+      <c r="F22" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="G22" s="54"/>
-      <c r="H22" s="54"/>
-      <c r="I22" s="55"/>
+      <c r="G22" s="79"/>
+      <c r="H22" s="79"/>
+      <c r="I22" s="80"/>
       <c r="J22" s="28"/>
-      <c r="K22" s="57"/>
-      <c r="L22" s="29"/>
-      <c r="M22" s="30"/>
+      <c r="K22" s="36"/>
+      <c r="L22" s="96"/>
+      <c r="M22" s="97"/>
       <c r="N22" s="24"/>
       <c r="O22" s="11"/>
-      <c r="P22" s="53" t="s">
+      <c r="P22" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="Q22" s="54"/>
-      <c r="R22" s="54"/>
-      <c r="S22" s="55"/>
+      <c r="Q22" s="79"/>
+      <c r="R22" s="79"/>
+      <c r="S22" s="80"/>
       <c r="T22" s="27"/>
     </row>
     <row r="23" spans="1:20" ht="29.25" customHeight="1" thickBot="1">
-      <c r="A23" s="58"/>
-      <c r="B23" s="40" t="s">
+      <c r="A23" s="37"/>
+      <c r="B23" s="91" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="41"/>
-      <c r="D23" s="38" t="s">
+      <c r="C23" s="92"/>
+      <c r="D23" s="93" t="s">
         <v>27</v>
       </c>
-      <c r="E23" s="41"/>
-      <c r="F23" s="42" t="s">
+      <c r="E23" s="92"/>
+      <c r="F23" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="G23" s="43"/>
-      <c r="H23" s="38" t="s">
+      <c r="G23" s="95"/>
+      <c r="H23" s="93" t="s">
         <v>29</v>
       </c>
-      <c r="I23" s="39"/>
-      <c r="K23" s="58"/>
-      <c r="L23" s="40" t="s">
+      <c r="I23" s="100"/>
+      <c r="K23" s="37"/>
+      <c r="L23" s="91" t="s">
         <v>28</v>
       </c>
-      <c r="M23" s="41"/>
-      <c r="N23" s="38" t="s">
+      <c r="M23" s="92"/>
+      <c r="N23" s="93" t="s">
         <v>27</v>
       </c>
-      <c r="O23" s="41"/>
-      <c r="P23" s="42" t="s">
+      <c r="O23" s="92"/>
+      <c r="P23" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="Q23" s="43"/>
-      <c r="R23" s="38" t="s">
+      <c r="Q23" s="95"/>
+      <c r="R23" s="93" t="s">
         <v>29</v>
       </c>
-      <c r="S23" s="39"/>
+      <c r="S23" s="100"/>
     </row>
     <row r="24" spans="1:20" ht="31.5" customHeight="1">
       <c r="A24" s="18" t="s">
@@ -3021,7 +2975,7 @@
       <c r="P24" s="23"/>
       <c r="Q24" s="23"/>
       <c r="R24" s="23"/>
-      <c r="S24" s="31" t="s">
+      <c r="S24" s="98" t="s">
         <v>18</v>
       </c>
       <c r="T24" s="26"/>
@@ -3044,19 +2998,60 @@
       <c r="P25" s="21"/>
       <c r="Q25" s="21"/>
       <c r="R25" s="21"/>
-      <c r="S25" s="32"/>
+      <c r="S25" s="99"/>
       <c r="T25" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="73">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="K1:S1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="K2:S2"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="K3:K5"/>
-    <mergeCell ref="L3:S3"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="S24:S25"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="P21:S21"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="A6:A19"/>
+    <mergeCell ref="R9:S9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="P22:S22"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="B20:I20"/>
+    <mergeCell ref="K20:K23"/>
+    <mergeCell ref="L20:S20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="L17:L19"/>
+    <mergeCell ref="M17:N19"/>
+    <mergeCell ref="O17:P19"/>
+    <mergeCell ref="R17:R19"/>
+    <mergeCell ref="S17:S19"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="C17:D19"/>
+    <mergeCell ref="E17:F19"/>
+    <mergeCell ref="H17:H19"/>
+    <mergeCell ref="I17:I19"/>
+    <mergeCell ref="R11:R13"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:D16"/>
+    <mergeCell ref="E14:F16"/>
+    <mergeCell ref="H14:H16"/>
+    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="L14:L16"/>
+    <mergeCell ref="M14:N16"/>
+    <mergeCell ref="O14:P16"/>
+    <mergeCell ref="R14:R16"/>
+    <mergeCell ref="S14:S16"/>
     <mergeCell ref="M10:N10"/>
     <mergeCell ref="O10:P10"/>
     <mergeCell ref="B11:B13"/>
@@ -3073,55 +3068,14 @@
     <mergeCell ref="C9:F9"/>
     <mergeCell ref="H9:I9"/>
     <mergeCell ref="M9:P9"/>
-    <mergeCell ref="R11:R13"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:D16"/>
-    <mergeCell ref="E14:F16"/>
-    <mergeCell ref="H14:H16"/>
-    <mergeCell ref="I14:I16"/>
-    <mergeCell ref="L14:L16"/>
-    <mergeCell ref="M14:N16"/>
-    <mergeCell ref="O14:P16"/>
-    <mergeCell ref="R14:R16"/>
-    <mergeCell ref="S14:S16"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="C17:D19"/>
-    <mergeCell ref="E17:F19"/>
-    <mergeCell ref="H17:H19"/>
-    <mergeCell ref="I17:I19"/>
-    <mergeCell ref="L17:L19"/>
-    <mergeCell ref="M17:N19"/>
-    <mergeCell ref="O17:P19"/>
-    <mergeCell ref="R17:R19"/>
-    <mergeCell ref="S17:S19"/>
-    <mergeCell ref="A6:A19"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="P22:S22"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="B20:I20"/>
-    <mergeCell ref="K20:K23"/>
-    <mergeCell ref="L20:S20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="S24:S25"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="P21:S21"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="P23:Q23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="K1:S1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="K2:S2"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="K3:K5"/>
+    <mergeCell ref="L3:S3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/public/M15A上班時間調動表.xlsx
+++ b/public/M15A上班時間調動表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kyler\OneDrive\桌面\mss_ai_department\mss_ai_department\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEAD598C-6D96-424C-9003-3D74790E5452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{309CC543-E8EC-4953-B01D-D0522127765E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="599" xr2:uid="{99967081-488D-44D6-94DC-7450F6337A9B}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="30">
   <si>
     <t>處/機關：</t>
   </si>
@@ -46,10 +46,6 @@
   </si>
   <si>
     <t>原定上班時間</t>
-  </si>
-  <si>
-    <t>備註：</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Millennium Secondary School</t>
@@ -194,6 +190,9 @@
   <si>
     <t xml:space="preserve">                      年                      月                  日    </t>
   </si>
+  <si>
+    <t>備註：</t>
+  </si>
 </sst>
 </file>
 
@@ -1075,23 +1074,86 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
@@ -1102,32 +1164,86 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="37" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1135,34 +1251,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1183,8 +1275,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1192,137 +1296,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="37" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2328,85 +2327,85 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21.5">
-      <c r="A1" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="31"/>
-      <c r="K1" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="31"/>
+      <c r="A1" s="103" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="104"/>
+      <c r="C1" s="104"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="104"/>
+      <c r="F1" s="104"/>
+      <c r="G1" s="104"/>
+      <c r="H1" s="104"/>
+      <c r="I1" s="105"/>
+      <c r="K1" s="103" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="104"/>
+      <c r="M1" s="104"/>
+      <c r="N1" s="104"/>
+      <c r="O1" s="104"/>
+      <c r="P1" s="104"/>
+      <c r="Q1" s="104"/>
+      <c r="R1" s="104"/>
+      <c r="S1" s="105"/>
     </row>
     <row r="2" spans="1:19" ht="22" thickBot="1">
-      <c r="A2" s="32" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="34"/>
-      <c r="K2" s="32" t="s">
-        <v>7</v>
-      </c>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="34"/>
+      <c r="A2" s="106" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="107"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="107"/>
+      <c r="F2" s="107"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="107"/>
+      <c r="I2" s="108"/>
+      <c r="K2" s="106" t="s">
+        <v>6</v>
+      </c>
+      <c r="L2" s="107"/>
+      <c r="M2" s="107"/>
+      <c r="N2" s="107"/>
+      <c r="O2" s="107"/>
+      <c r="P2" s="107"/>
+      <c r="Q2" s="107"/>
+      <c r="R2" s="107"/>
+      <c r="S2" s="108"/>
     </row>
     <row r="3" spans="1:19" ht="25" customHeight="1">
-      <c r="A3" s="35">
+      <c r="A3" s="56">
         <v>1</v>
       </c>
-      <c r="B3" s="38" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="40"/>
-      <c r="K3" s="35">
+      <c r="B3" s="109" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="110"/>
+      <c r="D3" s="110"/>
+      <c r="E3" s="110"/>
+      <c r="F3" s="110"/>
+      <c r="G3" s="110"/>
+      <c r="H3" s="110"/>
+      <c r="I3" s="111"/>
+      <c r="K3" s="56">
         <v>1</v>
       </c>
-      <c r="L3" s="38" t="s">
-        <v>8</v>
-      </c>
-      <c r="M3" s="39"/>
-      <c r="N3" s="39"/>
-      <c r="O3" s="39"/>
-      <c r="P3" s="39"/>
-      <c r="Q3" s="39"/>
-      <c r="R3" s="39"/>
-      <c r="S3" s="40"/>
+      <c r="L3" s="109" t="s">
+        <v>7</v>
+      </c>
+      <c r="M3" s="110"/>
+      <c r="N3" s="110"/>
+      <c r="O3" s="110"/>
+      <c r="P3" s="110"/>
+      <c r="Q3" s="110"/>
+      <c r="R3" s="110"/>
+      <c r="S3" s="111"/>
     </row>
     <row r="4" spans="1:19" ht="25" customHeight="1">
-      <c r="A4" s="36"/>
+      <c r="A4" s="57"/>
       <c r="B4" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" s="19"/>
       <c r="D4" s="4"/>
@@ -2417,9 +2416,9 @@
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="5"/>
-      <c r="K4" s="36"/>
+      <c r="K4" s="57"/>
       <c r="L4" s="19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M4" s="19"/>
       <c r="N4" s="4"/>
@@ -2432,39 +2431,39 @@
       <c r="S4" s="5"/>
     </row>
     <row r="5" spans="1:19" ht="25" customHeight="1" thickBot="1">
-      <c r="A5" s="37"/>
+      <c r="A5" s="58"/>
       <c r="B5" s="21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5" s="21"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="21"/>
       <c r="G5" s="22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="3"/>
-      <c r="K5" s="37"/>
+      <c r="K5" s="58"/>
       <c r="L5" s="21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M5" s="21"/>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" s="21"/>
       <c r="Q5" s="22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R5" s="2"/>
       <c r="S5" s="3"/>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
-      <c r="A6" s="65">
+      <c r="A6" s="46">
         <v>2</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" s="15"/>
       <c r="D6" s="15"/>
@@ -2473,11 +2472,11 @@
       <c r="G6" s="15"/>
       <c r="H6" s="15"/>
       <c r="I6" s="16"/>
-      <c r="K6" s="65">
+      <c r="K6" s="46">
         <v>2</v>
       </c>
       <c r="L6" s="15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M6" s="15"/>
       <c r="N6" s="15"/>
@@ -2488,41 +2487,41 @@
       <c r="S6" s="16"/>
     </row>
     <row r="7" spans="1:19" ht="32.25" customHeight="1">
-      <c r="A7" s="65"/>
+      <c r="A7" s="46"/>
       <c r="B7" s="19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="101"/>
+      <c r="F7" s="101"/>
+      <c r="G7" s="101"/>
+      <c r="H7" s="101"/>
+      <c r="I7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="66"/>
-      <c r="F7" s="66"/>
-      <c r="G7" s="66"/>
-      <c r="H7" s="66"/>
-      <c r="I7" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K7" s="65"/>
+      <c r="K7" s="46"/>
       <c r="L7" s="19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M7" s="4"/>
       <c r="N7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="O7" s="101"/>
+      <c r="P7" s="101"/>
+      <c r="Q7" s="101"/>
+      <c r="R7" s="101"/>
+      <c r="S7" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="O7" s="66"/>
-      <c r="P7" s="66"/>
-      <c r="Q7" s="66"/>
-      <c r="R7" s="66"/>
-      <c r="S7" s="5" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="37.5" customHeight="1">
-      <c r="A8" s="65"/>
+      <c r="A8" s="46"/>
       <c r="B8" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" s="19"/>
       <c r="D8" s="4"/>
@@ -2531,9 +2530,9 @@
       <c r="G8" s="1"/>
       <c r="H8" s="4"/>
       <c r="I8" s="5"/>
-      <c r="K8" s="65"/>
+      <c r="K8" s="46"/>
       <c r="L8" s="19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M8" s="19"/>
       <c r="N8" s="4"/>
@@ -2544,44 +2543,44 @@
       <c r="S8" s="5"/>
     </row>
     <row r="9" spans="1:19" ht="25" customHeight="1">
-      <c r="A9" s="65"/>
+      <c r="A9" s="46"/>
       <c r="B9" s="19"/>
-      <c r="C9" s="67" t="s">
+      <c r="C9" s="102" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="52"/>
       <c r="G9" s="6"/>
-      <c r="H9" s="68" t="s">
+      <c r="H9" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="I9" s="69"/>
-      <c r="K9" s="65"/>
+      <c r="I9" s="48"/>
+      <c r="K9" s="46"/>
       <c r="L9" s="19"/>
-      <c r="M9" s="67" t="s">
+      <c r="M9" s="102" t="s">
         <v>4</v>
       </c>
-      <c r="N9" s="44"/>
-      <c r="O9" s="44"/>
-      <c r="P9" s="44"/>
+      <c r="N9" s="52"/>
+      <c r="O9" s="52"/>
+      <c r="P9" s="52"/>
       <c r="Q9" s="6"/>
-      <c r="R9" s="68" t="s">
+      <c r="R9" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="S9" s="69"/>
+      <c r="S9" s="48"/>
     </row>
     <row r="10" spans="1:19" ht="25" customHeight="1">
-      <c r="A10" s="65"/>
+      <c r="A10" s="46"/>
       <c r="B10" s="7"/>
-      <c r="C10" s="41" t="s">
+      <c r="C10" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="42"/>
-      <c r="E10" s="43" t="s">
+      <c r="D10" s="50"/>
+      <c r="E10" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="F10" s="44"/>
+      <c r="F10" s="52"/>
       <c r="G10" s="6"/>
       <c r="H10" s="8" t="s">
         <v>1</v>
@@ -2589,16 +2588,16 @@
       <c r="I10" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="K10" s="65"/>
+      <c r="K10" s="46"/>
       <c r="L10" s="7"/>
-      <c r="M10" s="41" t="s">
+      <c r="M10" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="N10" s="42"/>
-      <c r="O10" s="43" t="s">
+      <c r="N10" s="50"/>
+      <c r="O10" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="P10" s="44"/>
+      <c r="P10" s="52"/>
       <c r="Q10" s="6"/>
       <c r="R10" s="8" t="s">
         <v>1</v>
@@ -2608,353 +2607,350 @@
       </c>
     </row>
     <row r="11" spans="1:19" ht="28" customHeight="1">
-      <c r="A11" s="65"/>
-      <c r="B11" s="45">
+      <c r="A11" s="46"/>
+      <c r="B11" s="62">
         <v>1</v>
       </c>
-      <c r="C11" s="101" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="102"/>
-      <c r="E11" s="48"/>
-      <c r="F11" s="49"/>
+      <c r="C11" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="96"/>
+      <c r="E11" s="87"/>
+      <c r="F11" s="72"/>
       <c r="G11" s="10"/>
-      <c r="H11" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="I11" s="57"/>
-      <c r="K11" s="65"/>
-      <c r="L11" s="45">
+      <c r="H11" s="77" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="83"/>
+      <c r="K11" s="46"/>
+      <c r="L11" s="62">
         <v>1</v>
       </c>
-      <c r="M11" s="101" t="str">
-        <f>C11</f>
-        <v xml:space="preserve"> 年  月  日</v>
-      </c>
-      <c r="N11" s="107"/>
-      <c r="O11" s="48"/>
-      <c r="P11" s="60"/>
+      <c r="M11" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="N11" s="66"/>
+      <c r="O11" s="87"/>
+      <c r="P11" s="91"/>
       <c r="Q11" s="10"/>
-      <c r="R11" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="S11" s="57"/>
+      <c r="R11" s="77" t="s">
+        <v>25</v>
+      </c>
+      <c r="S11" s="83"/>
     </row>
     <row r="12" spans="1:19" ht="28" customHeight="1">
-      <c r="A12" s="65"/>
-      <c r="B12" s="46"/>
-      <c r="C12" s="103"/>
-      <c r="D12" s="104"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="51"/>
+      <c r="A12" s="46"/>
+      <c r="B12" s="63"/>
+      <c r="C12" s="97"/>
+      <c r="D12" s="98"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="74"/>
       <c r="G12" s="12"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="58"/>
-      <c r="K12" s="65"/>
-      <c r="L12" s="46"/>
-      <c r="M12" s="108"/>
-      <c r="N12" s="109"/>
-      <c r="O12" s="61"/>
-      <c r="P12" s="62"/>
+      <c r="H12" s="78"/>
+      <c r="I12" s="81"/>
+      <c r="K12" s="46"/>
+      <c r="L12" s="63"/>
+      <c r="M12" s="67"/>
+      <c r="N12" s="68"/>
+      <c r="O12" s="92"/>
+      <c r="P12" s="93"/>
       <c r="Q12" s="12"/>
-      <c r="R12" s="55"/>
-      <c r="S12" s="70"/>
+      <c r="R12" s="78"/>
+      <c r="S12" s="84"/>
     </row>
     <row r="13" spans="1:19" ht="28" customHeight="1">
-      <c r="A13" s="65"/>
-      <c r="B13" s="47"/>
-      <c r="C13" s="105"/>
-      <c r="D13" s="106"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="53"/>
+      <c r="A13" s="46"/>
+      <c r="B13" s="86"/>
+      <c r="C13" s="99"/>
+      <c r="D13" s="100"/>
+      <c r="E13" s="88"/>
+      <c r="F13" s="89"/>
       <c r="G13" s="11"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="59"/>
-      <c r="K13" s="65"/>
-      <c r="L13" s="47"/>
-      <c r="M13" s="110"/>
-      <c r="N13" s="111"/>
-      <c r="O13" s="63"/>
-      <c r="P13" s="64"/>
+      <c r="H13" s="79"/>
+      <c r="I13" s="90"/>
+      <c r="K13" s="46"/>
+      <c r="L13" s="86"/>
+      <c r="M13" s="69"/>
+      <c r="N13" s="70"/>
+      <c r="O13" s="94"/>
+      <c r="P13" s="95"/>
       <c r="Q13" s="11"/>
-      <c r="R13" s="56"/>
-      <c r="S13" s="71"/>
+      <c r="R13" s="79"/>
+      <c r="S13" s="85"/>
     </row>
     <row r="14" spans="1:19" ht="28" customHeight="1">
-      <c r="A14" s="65"/>
-      <c r="B14" s="45">
+      <c r="A14" s="46"/>
+      <c r="B14" s="62">
         <v>2</v>
       </c>
-      <c r="C14" s="101" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="107"/>
-      <c r="E14" s="48"/>
-      <c r="F14" s="49"/>
+      <c r="C14" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="66"/>
+      <c r="E14" s="87"/>
+      <c r="F14" s="72"/>
       <c r="G14" s="10"/>
-      <c r="H14" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="I14" s="57"/>
-      <c r="K14" s="65"/>
-      <c r="L14" s="45">
+      <c r="H14" s="77" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14" s="83"/>
+      <c r="K14" s="46"/>
+      <c r="L14" s="62">
         <v>2</v>
       </c>
-      <c r="M14" s="101" t="str">
-        <f>C14</f>
-        <v xml:space="preserve"> 年  月  日</v>
-      </c>
-      <c r="N14" s="107"/>
-      <c r="O14" s="48"/>
-      <c r="P14" s="60"/>
+      <c r="M14" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="N14" s="66"/>
+      <c r="O14" s="87"/>
+      <c r="P14" s="91"/>
       <c r="Q14" s="10"/>
-      <c r="R14" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="S14" s="57"/>
+      <c r="R14" s="77" t="s">
+        <v>25</v>
+      </c>
+      <c r="S14" s="83"/>
     </row>
     <row r="15" spans="1:19" ht="28" customHeight="1">
-      <c r="A15" s="65"/>
-      <c r="B15" s="46"/>
-      <c r="C15" s="108"/>
-      <c r="D15" s="109"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="51"/>
+      <c r="A15" s="46"/>
+      <c r="B15" s="63"/>
+      <c r="C15" s="67"/>
+      <c r="D15" s="68"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="74"/>
       <c r="G15" s="12"/>
-      <c r="H15" s="55"/>
-      <c r="I15" s="58"/>
-      <c r="K15" s="65"/>
-      <c r="L15" s="46"/>
-      <c r="M15" s="108"/>
-      <c r="N15" s="109"/>
-      <c r="O15" s="61"/>
-      <c r="P15" s="62"/>
+      <c r="H15" s="78"/>
+      <c r="I15" s="81"/>
+      <c r="K15" s="46"/>
+      <c r="L15" s="63"/>
+      <c r="M15" s="67"/>
+      <c r="N15" s="68"/>
+      <c r="O15" s="92"/>
+      <c r="P15" s="93"/>
       <c r="Q15" s="12"/>
-      <c r="R15" s="55"/>
-      <c r="S15" s="70"/>
+      <c r="R15" s="78"/>
+      <c r="S15" s="84"/>
     </row>
     <row r="16" spans="1:19" ht="28" customHeight="1">
-      <c r="A16" s="65"/>
-      <c r="B16" s="47"/>
-      <c r="C16" s="110"/>
-      <c r="D16" s="111"/>
-      <c r="E16" s="52"/>
-      <c r="F16" s="53"/>
+      <c r="A16" s="46"/>
+      <c r="B16" s="86"/>
+      <c r="C16" s="69"/>
+      <c r="D16" s="70"/>
+      <c r="E16" s="88"/>
+      <c r="F16" s="89"/>
       <c r="G16" s="11"/>
-      <c r="H16" s="56"/>
-      <c r="I16" s="59"/>
-      <c r="K16" s="65"/>
-      <c r="L16" s="47"/>
-      <c r="M16" s="110"/>
-      <c r="N16" s="111"/>
-      <c r="O16" s="63"/>
-      <c r="P16" s="64"/>
+      <c r="H16" s="79"/>
+      <c r="I16" s="90"/>
+      <c r="K16" s="46"/>
+      <c r="L16" s="86"/>
+      <c r="M16" s="69"/>
+      <c r="N16" s="70"/>
+      <c r="O16" s="94"/>
+      <c r="P16" s="95"/>
       <c r="Q16" s="11"/>
-      <c r="R16" s="56"/>
-      <c r="S16" s="71"/>
+      <c r="R16" s="79"/>
+      <c r="S16" s="85"/>
     </row>
     <row r="17" spans="1:20" ht="28" customHeight="1">
-      <c r="A17" s="65"/>
-      <c r="B17" s="45">
+      <c r="A17" s="46"/>
+      <c r="B17" s="62">
         <v>3</v>
       </c>
-      <c r="C17" s="101" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17" s="107"/>
-      <c r="E17" s="73"/>
-      <c r="F17" s="49"/>
+      <c r="C17" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="66"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="72"/>
       <c r="G17" s="10"/>
-      <c r="H17" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="I17" s="57"/>
-      <c r="K17" s="65"/>
-      <c r="L17" s="45">
+      <c r="H17" s="77" t="s">
+        <v>25</v>
+      </c>
+      <c r="I17" s="83"/>
+      <c r="K17" s="46"/>
+      <c r="L17" s="62">
         <v>3</v>
       </c>
-      <c r="M17" s="101" t="str">
-        <f>C17</f>
-        <v xml:space="preserve"> 年  月  日</v>
-      </c>
-      <c r="N17" s="107"/>
-      <c r="O17" s="73"/>
-      <c r="P17" s="49"/>
+      <c r="M17" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="N17" s="66"/>
+      <c r="O17" s="71"/>
+      <c r="P17" s="72"/>
       <c r="Q17" s="10"/>
-      <c r="R17" s="54" t="s">
-        <v>26</v>
-      </c>
-      <c r="S17" s="77"/>
+      <c r="R17" s="77" t="s">
+        <v>25</v>
+      </c>
+      <c r="S17" s="80"/>
     </row>
     <row r="18" spans="1:20" ht="28" customHeight="1">
-      <c r="A18" s="65"/>
-      <c r="B18" s="46"/>
-      <c r="C18" s="108"/>
-      <c r="D18" s="109"/>
-      <c r="E18" s="50"/>
-      <c r="F18" s="51"/>
+      <c r="A18" s="46"/>
+      <c r="B18" s="63"/>
+      <c r="C18" s="67"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="73"/>
+      <c r="F18" s="74"/>
       <c r="G18" s="12"/>
-      <c r="H18" s="55"/>
-      <c r="I18" s="58"/>
-      <c r="K18" s="65"/>
-      <c r="L18" s="46"/>
-      <c r="M18" s="108"/>
-      <c r="N18" s="109"/>
-      <c r="O18" s="50"/>
-      <c r="P18" s="51"/>
+      <c r="H18" s="78"/>
+      <c r="I18" s="81"/>
+      <c r="K18" s="46"/>
+      <c r="L18" s="63"/>
+      <c r="M18" s="67"/>
+      <c r="N18" s="68"/>
+      <c r="O18" s="73"/>
+      <c r="P18" s="74"/>
       <c r="Q18" s="12"/>
-      <c r="R18" s="55"/>
-      <c r="S18" s="58"/>
+      <c r="R18" s="78"/>
+      <c r="S18" s="81"/>
     </row>
     <row r="19" spans="1:20" ht="28" customHeight="1" thickBot="1">
-      <c r="A19" s="65"/>
-      <c r="B19" s="72"/>
-      <c r="C19" s="110"/>
-      <c r="D19" s="111"/>
-      <c r="E19" s="74"/>
-      <c r="F19" s="75"/>
+      <c r="A19" s="46"/>
+      <c r="B19" s="64"/>
+      <c r="C19" s="69"/>
+      <c r="D19" s="70"/>
+      <c r="E19" s="75"/>
+      <c r="F19" s="76"/>
       <c r="G19" s="13"/>
-      <c r="H19" s="56"/>
-      <c r="I19" s="76"/>
-      <c r="K19" s="65"/>
-      <c r="L19" s="72"/>
-      <c r="M19" s="110"/>
-      <c r="N19" s="111"/>
-      <c r="O19" s="74"/>
-      <c r="P19" s="75"/>
+      <c r="H19" s="79"/>
+      <c r="I19" s="82"/>
+      <c r="K19" s="46"/>
+      <c r="L19" s="64"/>
+      <c r="M19" s="69"/>
+      <c r="N19" s="70"/>
+      <c r="O19" s="75"/>
+      <c r="P19" s="76"/>
       <c r="Q19" s="13"/>
-      <c r="R19" s="56"/>
-      <c r="S19" s="76"/>
+      <c r="R19" s="79"/>
+      <c r="S19" s="82"/>
     </row>
     <row r="20" spans="1:20" ht="20.25" customHeight="1">
-      <c r="A20" s="35">
+      <c r="A20" s="56">
         <v>3</v>
       </c>
-      <c r="B20" s="81" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" s="82"/>
-      <c r="D20" s="82"/>
-      <c r="E20" s="82"/>
-      <c r="F20" s="82"/>
-      <c r="G20" s="82"/>
-      <c r="H20" s="82"/>
-      <c r="I20" s="83"/>
-      <c r="K20" s="35">
+      <c r="B20" s="59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="60"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60"/>
+      <c r="H20" s="60"/>
+      <c r="I20" s="61"/>
+      <c r="K20" s="56">
         <v>3</v>
       </c>
-      <c r="L20" s="81" t="s">
-        <v>17</v>
-      </c>
-      <c r="M20" s="82"/>
-      <c r="N20" s="82"/>
-      <c r="O20" s="82"/>
-      <c r="P20" s="82"/>
-      <c r="Q20" s="82"/>
-      <c r="R20" s="82"/>
-      <c r="S20" s="83"/>
+      <c r="L20" s="59" t="s">
+        <v>16</v>
+      </c>
+      <c r="M20" s="60"/>
+      <c r="N20" s="60"/>
+      <c r="O20" s="60"/>
+      <c r="P20" s="60"/>
+      <c r="Q20" s="60"/>
+      <c r="R20" s="60"/>
+      <c r="S20" s="61"/>
     </row>
     <row r="21" spans="1:20" ht="45" customHeight="1">
-      <c r="A21" s="36"/>
-      <c r="B21" s="84" t="s">
+      <c r="A21" s="57"/>
+      <c r="B21" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="45"/>
+      <c r="D21" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="85"/>
-      <c r="D21" s="86" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21" s="87"/>
-      <c r="F21" s="88" t="s">
+      <c r="E21" s="34"/>
+      <c r="F21" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="36"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="37"/>
+      <c r="K21" s="57"/>
+      <c r="L21" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="G21" s="89"/>
-      <c r="H21" s="89"/>
-      <c r="I21" s="90"/>
-      <c r="K21" s="36"/>
-      <c r="L21" s="84" t="s">
+      <c r="M21" s="45"/>
+      <c r="N21" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="M21" s="85"/>
-      <c r="N21" s="86" t="s">
-        <v>22</v>
-      </c>
-      <c r="O21" s="87"/>
-      <c r="P21" s="88" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q21" s="89"/>
-      <c r="R21" s="89"/>
-      <c r="S21" s="90"/>
+      <c r="O21" s="34"/>
+      <c r="P21" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="36"/>
+      <c r="S21" s="37"/>
     </row>
     <row r="22" spans="1:20" ht="63.75" customHeight="1">
-      <c r="A22" s="36"/>
-      <c r="B22" s="96"/>
-      <c r="C22" s="97"/>
+      <c r="A22" s="57"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="30"/>
       <c r="D22" s="24"/>
       <c r="E22" s="11"/>
-      <c r="F22" s="78" t="s">
-        <v>24</v>
-      </c>
-      <c r="G22" s="79"/>
-      <c r="H22" s="79"/>
-      <c r="I22" s="80"/>
+      <c r="F22" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" s="54"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="55"/>
       <c r="J22" s="28"/>
-      <c r="K22" s="36"/>
-      <c r="L22" s="96"/>
-      <c r="M22" s="97"/>
+      <c r="K22" s="57"/>
+      <c r="L22" s="29"/>
+      <c r="M22" s="30"/>
       <c r="N22" s="24"/>
       <c r="O22" s="11"/>
-      <c r="P22" s="78" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q22" s="79"/>
-      <c r="R22" s="79"/>
-      <c r="S22" s="80"/>
+      <c r="P22" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q22" s="54"/>
+      <c r="R22" s="54"/>
+      <c r="S22" s="55"/>
       <c r="T22" s="27"/>
     </row>
     <row r="23" spans="1:20" ht="29.25" customHeight="1" thickBot="1">
-      <c r="A23" s="37"/>
-      <c r="B23" s="91" t="s">
+      <c r="A23" s="58"/>
+      <c r="B23" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="41"/>
+      <c r="D23" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="41"/>
+      <c r="F23" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" s="43"/>
+      <c r="H23" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="92"/>
-      <c r="D23" s="93" t="s">
+      <c r="I23" s="39"/>
+      <c r="K23" s="58"/>
+      <c r="L23" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="E23" s="92"/>
-      <c r="F23" s="94" t="s">
-        <v>19</v>
-      </c>
-      <c r="G23" s="95"/>
-      <c r="H23" s="93" t="s">
-        <v>29</v>
-      </c>
-      <c r="I23" s="100"/>
-      <c r="K23" s="37"/>
-      <c r="L23" s="91" t="s">
+      <c r="M23" s="41"/>
+      <c r="N23" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="O23" s="41"/>
+      <c r="P23" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q23" s="43"/>
+      <c r="R23" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="M23" s="92"/>
-      <c r="N23" s="93" t="s">
-        <v>27</v>
-      </c>
-      <c r="O23" s="92"/>
-      <c r="P23" s="94" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q23" s="95"/>
-      <c r="R23" s="93" t="s">
-        <v>29</v>
-      </c>
-      <c r="S23" s="100"/>
+      <c r="S23" s="39"/>
     </row>
     <row r="24" spans="1:20" ht="31.5" customHeight="1">
       <c r="A24" s="18" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="B24" s="23"/>
       <c r="C24" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D24" s="23"/>
       <c r="E24" s="23"/>
@@ -2963,20 +2959,19 @@
       <c r="H24" s="23"/>
       <c r="I24" s="25"/>
       <c r="K24" s="18" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="L24" s="23"/>
-      <c r="M24" s="23" t="str">
-        <f>C24</f>
-        <v>不涉及課堂</v>
+      <c r="M24" s="23" t="s">
+        <v>24</v>
       </c>
       <c r="N24" s="23"/>
       <c r="O24" s="23"/>
       <c r="P24" s="23"/>
       <c r="Q24" s="23"/>
       <c r="R24" s="23"/>
-      <c r="S24" s="98" t="s">
-        <v>18</v>
+      <c r="S24" s="31" t="s">
+        <v>17</v>
       </c>
       <c r="T24" s="26"/>
     </row>
@@ -2998,22 +2993,57 @@
       <c r="P25" s="21"/>
       <c r="Q25" s="21"/>
       <c r="R25" s="21"/>
-      <c r="S25" s="99"/>
+      <c r="S25" s="32"/>
       <c r="T25" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="73">
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="S24:S25"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="P21:S21"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="P23:Q23"/>
-    <mergeCell ref="R23:S23"/>
-    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="K1:S1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="K2:S2"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="K3:K5"/>
+    <mergeCell ref="L3:S3"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:D13"/>
+    <mergeCell ref="E11:F13"/>
+    <mergeCell ref="H11:H13"/>
+    <mergeCell ref="I11:I13"/>
+    <mergeCell ref="L11:L13"/>
+    <mergeCell ref="M11:N13"/>
+    <mergeCell ref="O11:P13"/>
+    <mergeCell ref="K6:K19"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="O7:R7"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="M9:P9"/>
+    <mergeCell ref="R11:R13"/>
+    <mergeCell ref="S11:S13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="C14:D16"/>
+    <mergeCell ref="E14:F16"/>
+    <mergeCell ref="H14:H16"/>
+    <mergeCell ref="I14:I16"/>
+    <mergeCell ref="L14:L16"/>
+    <mergeCell ref="M14:N16"/>
+    <mergeCell ref="O14:P16"/>
+    <mergeCell ref="R14:R16"/>
+    <mergeCell ref="S14:S16"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="C17:D19"/>
+    <mergeCell ref="E17:F19"/>
+    <mergeCell ref="H17:H19"/>
+    <mergeCell ref="I17:I19"/>
+    <mergeCell ref="L17:L19"/>
+    <mergeCell ref="M17:N19"/>
+    <mergeCell ref="O17:P19"/>
+    <mergeCell ref="R17:R19"/>
+    <mergeCell ref="S17:S19"/>
     <mergeCell ref="A6:A19"/>
     <mergeCell ref="R9:S9"/>
     <mergeCell ref="C10:D10"/>
@@ -3030,52 +3060,17 @@
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="D23:E23"/>
     <mergeCell ref="F23:G23"/>
-    <mergeCell ref="L17:L19"/>
-    <mergeCell ref="M17:N19"/>
-    <mergeCell ref="O17:P19"/>
-    <mergeCell ref="R17:R19"/>
-    <mergeCell ref="S17:S19"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="C17:D19"/>
-    <mergeCell ref="E17:F19"/>
-    <mergeCell ref="H17:H19"/>
-    <mergeCell ref="I17:I19"/>
-    <mergeCell ref="R11:R13"/>
-    <mergeCell ref="S11:S13"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="C14:D16"/>
-    <mergeCell ref="E14:F16"/>
-    <mergeCell ref="H14:H16"/>
-    <mergeCell ref="I14:I16"/>
-    <mergeCell ref="L14:L16"/>
-    <mergeCell ref="M14:N16"/>
-    <mergeCell ref="O14:P16"/>
-    <mergeCell ref="R14:R16"/>
-    <mergeCell ref="S14:S16"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="O10:P10"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="C11:D13"/>
-    <mergeCell ref="E11:F13"/>
-    <mergeCell ref="H11:H13"/>
-    <mergeCell ref="I11:I13"/>
-    <mergeCell ref="L11:L13"/>
-    <mergeCell ref="M11:N13"/>
-    <mergeCell ref="O11:P13"/>
-    <mergeCell ref="K6:K19"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="O7:R7"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="M9:P9"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="K1:S1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="K2:S2"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="K3:K5"/>
-    <mergeCell ref="L3:S3"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="S24:S25"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="P21:S21"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="R23:S23"/>
+    <mergeCell ref="L21:M21"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
